--- a/files/Client_Scenarios_Data_File.xlsx
+++ b/files/Client_Scenarios_Data_File.xlsx
@@ -741,9 +741,9 @@
   <cols>
     <col min="1" max="1" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.88671875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="7.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32.21875" bestFit="1" customWidth="1"/>
@@ -1426,6 +1426,158 @@
         <v>Risk Seeking</v>
       </c>
     </row>
+    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>6</v>
+      </c>
+      <c r="B17" s="7">
+        <v>16</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Nora Ellis</t>
+        </is>
+      </c>
+      <c r="D17" s="9">
+        <v>61</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Occupational Therapist</t>
+        </is>
+      </c>
+      <c r="F17" s="6">
+        <v>95000</v>
+      </c>
+      <c r="G17" s="6">
+        <v>900000</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Family Care / Capital Preservation</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>$90k access work in 2 yrs; care reserve</t>
+        </is>
+      </c>
+      <c r="J17" s="4">
+        <v>0.045</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="L17" s="5">
+        <v>8</v>
+      </c>
+      <c r="M17" s="5" t="str">
+        <f>IF(L17&gt;4.5,"Risk Averse",IF(L17&lt;=2.5,"Risk Seeking","Risk Neutral"))</f>
+        <v>Risk Averse</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>6</v>
+      </c>
+      <c r="B18" s="7">
+        <v>17</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Priya &amp; Owen Brooks</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>40/42</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Engineer / School Administrator</t>
+        </is>
+      </c>
+      <c r="F18" s="6">
+        <v>205000</v>
+      </c>
+      <c r="G18" s="6">
+        <v>780000</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Career Break / Retirement</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>$100k career break in 4 yrs; 20-yr retirement</t>
+        </is>
+      </c>
+      <c r="J18" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="L18" s="5">
+        <v>4</v>
+      </c>
+      <c r="M18" s="5" t="str">
+        <f>IF(L18&gt;4.5,"Risk Averse",IF(L18&lt;=2.5,"Risk Seeking","Risk Neutral"))</f>
+        <v>Risk Neutral</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>6</v>
+      </c>
+      <c r="B19" s="7">
+        <v>18</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Adrian Cole</t>
+        </is>
+      </c>
+      <c r="D19" s="9">
+        <v>35</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Airline Pilot</t>
+        </is>
+      </c>
+      <c r="F19" s="6">
+        <v>180000</v>
+      </c>
+      <c r="G19" s="6">
+        <v>650000</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Long-term Financial Independence</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>25-yr horizon; cash reserve outside portfolio</t>
+        </is>
+      </c>
+      <c r="J19" s="4">
+        <v>0.095</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="L19" s="5">
+        <v>2</v>
+      </c>
+      <c r="M19" s="5" t="str">
+        <f>IF(L19&gt;4.5,"Risk Averse",IF(L19&lt;=2.5,"Risk Seeking","Risk Neutral"))</f>
+        <v>Risk Seeking</v>
+      </c>
+    </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20"/>
       <c r="B20"/>
@@ -1548,7 +1700,7 @@
       <c r="B46"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M16" xr:uid="{99D5CFF8-450C-4967-A153-7C927162598A}"/>
+  <autoFilter ref="A1:M19" xr:uid="{99D5CFF8-450C-4967-A153-7C927162598A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>